--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K636"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25236,6 +25236,84 @@
         <v>354.75</v>
       </c>
       <c r="K636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="C637" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="D637" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="E637" t="n">
+        <v>360.61</v>
+      </c>
+      <c r="F637" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="G637" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="H637" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="I637" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="J637" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>365.12</v>
+      </c>
+      <c r="C638" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="D638" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="E638" t="n">
+        <v>360.68</v>
+      </c>
+      <c r="F638" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="G638" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="H638" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="I638" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="J638" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="K638" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25252,7 +25330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31805,6 +31883,16 @@
       </c>
       <c r="B655" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -31973,28 +32061,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2749969578579425</v>
+        <v>-0.2742381299226002</v>
       </c>
       <c r="J2" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2901028074639836</v>
+        <v>0.2902810300699459</v>
       </c>
       <c r="M2" t="n">
-        <v>2.583916777546414</v>
+        <v>2.579812127159963</v>
       </c>
       <c r="N2" t="n">
-        <v>9.841844921335007</v>
+        <v>9.815453333068872</v>
       </c>
       <c r="O2" t="n">
-        <v>3.137171484209145</v>
+        <v>3.132962389347959</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3850808873106</v>
+        <v>371.3770994422774</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32055,28 +32143,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2137857643712053</v>
+        <v>-0.2124712100099892</v>
       </c>
       <c r="J3" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.249313498675219</v>
+        <v>0.2479487267323072</v>
       </c>
       <c r="M3" t="n">
-        <v>2.26934571075947</v>
+        <v>2.269286245287715</v>
       </c>
       <c r="N3" t="n">
-        <v>7.318929952438062</v>
+        <v>7.309247668705829</v>
       </c>
       <c r="O3" t="n">
-        <v>2.70535209398667</v>
+        <v>2.703562033448804</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5790631376962</v>
+        <v>366.5652353490507</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32137,28 +32225,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1879383804767783</v>
+        <v>-0.1870769822796965</v>
       </c>
       <c r="J4" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2570530418785135</v>
+        <v>0.2564093884049521</v>
       </c>
       <c r="M4" t="n">
-        <v>1.883873111301881</v>
+        <v>1.882260146251459</v>
       </c>
       <c r="N4" t="n">
-        <v>5.407588275931742</v>
+        <v>5.396346343833828</v>
       </c>
       <c r="O4" t="n">
-        <v>2.325422171549016</v>
+        <v>2.323003733064979</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1351634315471</v>
+        <v>368.1260913380476</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32219,28 +32307,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2226980360554343</v>
+        <v>-0.2237614130041332</v>
       </c>
       <c r="J5" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K5" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3749576966854044</v>
+        <v>0.378341203679189</v>
       </c>
       <c r="M5" t="n">
-        <v>1.684413898878181</v>
+        <v>1.683557653001177</v>
       </c>
       <c r="N5" t="n">
-        <v>4.379227521068465</v>
+        <v>4.374193215001391</v>
       </c>
       <c r="O5" t="n">
-        <v>2.09266039315233</v>
+        <v>2.091457198940823</v>
       </c>
       <c r="P5" t="n">
-        <v>368.160128664694</v>
+        <v>368.1713275229891</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32301,28 +32389,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2533884075166538</v>
+        <v>-0.2547261020164821</v>
       </c>
       <c r="J6" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K6" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3742876276072911</v>
+        <v>0.3778023569155489</v>
       </c>
       <c r="M6" t="n">
-        <v>1.96735192082564</v>
+        <v>1.968718423941066</v>
       </c>
       <c r="N6" t="n">
-        <v>5.685653009544486</v>
+        <v>5.681587863021542</v>
       </c>
       <c r="O6" t="n">
-        <v>2.384460737681476</v>
+        <v>2.383608160546012</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1336570461841</v>
+        <v>371.1477450807234</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32383,28 +32471,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1272255443638762</v>
+        <v>-0.1267769917996452</v>
       </c>
       <c r="J7" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K7" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08399664828330611</v>
+        <v>0.08396938649182295</v>
       </c>
       <c r="M7" t="n">
-        <v>2.428784603311332</v>
+        <v>2.423577308304087</v>
       </c>
       <c r="N7" t="n">
-        <v>9.350209415696463</v>
+        <v>9.322427653876231</v>
       </c>
       <c r="O7" t="n">
-        <v>3.057811213220408</v>
+        <v>3.053265080839892</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5763407379829</v>
+        <v>371.5716170831773</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32465,28 +32553,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1184107417304917</v>
+        <v>-0.1204923816829739</v>
       </c>
       <c r="J8" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K8" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1054766658219525</v>
+        <v>0.1089628714164752</v>
       </c>
       <c r="M8" t="n">
-        <v>1.823916189911622</v>
+        <v>1.828252981356397</v>
       </c>
       <c r="N8" t="n">
-        <v>6.298760280941859</v>
+        <v>6.312415364658253</v>
       </c>
       <c r="O8" t="n">
-        <v>2.509733109504247</v>
+        <v>2.512452062161237</v>
       </c>
       <c r="P8" t="n">
-        <v>373.3390515037615</v>
+        <v>373.3609747523084</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32547,28 +32635,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1305505954957881</v>
+        <v>-0.131461939384212</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K9" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0945852244761638</v>
+        <v>0.09631616599553849</v>
       </c>
       <c r="M9" t="n">
-        <v>2.385189728477428</v>
+        <v>2.382423502259337</v>
       </c>
       <c r="N9" t="n">
-        <v>8.642106006709669</v>
+        <v>8.621374793836541</v>
       </c>
       <c r="O9" t="n">
-        <v>2.939745908528434</v>
+        <v>2.93621777016565</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1308081891056</v>
+        <v>368.1404059070097</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32629,28 +32717,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1927577338660738</v>
+        <v>-0.196073681433445</v>
       </c>
       <c r="J10" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K10" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1369572066377521</v>
+        <v>0.1410452181320606</v>
       </c>
       <c r="M10" t="n">
-        <v>2.771429803745237</v>
+        <v>2.779574874228032</v>
       </c>
       <c r="N10" t="n">
-        <v>12.40248358565744</v>
+        <v>12.44828922265273</v>
       </c>
       <c r="O10" t="n">
-        <v>3.521716000142181</v>
+        <v>3.528213318756779</v>
       </c>
       <c r="P10" t="n">
-        <v>364.8968214710114</v>
+        <v>364.9317438293558</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32692,7 +32780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K636"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68923,6 +69011,120 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.62208064936215,174.7658968596667</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.62178484460014,174.76671663205653</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.621451550844746,174.7675062867357</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.62103875105196,174.76823909382256</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.620583991822315,174.7689347950795</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-36.620053213941425,174.76953272420798</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-36.619533932535866,174.77013820136244</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-36.61893308734265,174.77062396388428</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>-36.618347152743056,174.77115773249065</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.62208467413649,174.76589937358247</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.621786047413345,174.76671739750284</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.62145034319779,174.76750530925443</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.62103825834321,174.76823860506835</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.62058439816424,174.7689352376641</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.62005439111973,174.7695342668379</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.61953533179322,174.77014067095615</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-36.6189327775026,174.77062328217997</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>-36.61834825930715,174.77116016713524</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K638"/>
+  <dimension ref="A1:K639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25316,6 +25316,45 @@
       <c r="K638" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="C639" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="D639" t="n">
+        <v>364.55</v>
+      </c>
+      <c r="E639" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="F639" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="G639" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="H639" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="I639" t="n">
+        <v>363.42</v>
+      </c>
+      <c r="J639" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25330,7 +25369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B656"/>
+  <dimension ref="A1:B657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31893,6 +31932,16 @@
       </c>
       <c r="B656" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>
@@ -32061,28 +32110,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2742381299226002</v>
+        <v>-0.2740644447735591</v>
       </c>
       <c r="J2" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2902810300699459</v>
+        <v>0.2907174275007122</v>
       </c>
       <c r="M2" t="n">
-        <v>2.579812127159963</v>
+        <v>2.57667756320093</v>
       </c>
       <c r="N2" t="n">
-        <v>9.815453333068872</v>
+        <v>9.800465163077305</v>
       </c>
       <c r="O2" t="n">
-        <v>3.132962389347959</v>
+        <v>3.130569463065355</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3770994422774</v>
+        <v>371.3752682607205</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32143,28 +32192,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2124712100099892</v>
+        <v>-0.2118715907308826</v>
       </c>
       <c r="J3" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2479487267323072</v>
+        <v>0.247392343130342</v>
       </c>
       <c r="M3" t="n">
-        <v>2.269286245287715</v>
+        <v>2.268947297686434</v>
       </c>
       <c r="N3" t="n">
-        <v>7.309247668705829</v>
+        <v>7.303329695773823</v>
       </c>
       <c r="O3" t="n">
-        <v>2.703562033448804</v>
+        <v>2.702467334820871</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5652353490507</v>
+        <v>366.5589134972913</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32225,28 +32274,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1870769822796965</v>
+        <v>-0.1866513768508461</v>
       </c>
       <c r="J4" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2564093884049521</v>
+        <v>0.256097466155993</v>
       </c>
       <c r="M4" t="n">
-        <v>1.882260146251459</v>
+        <v>1.881439949222615</v>
       </c>
       <c r="N4" t="n">
-        <v>5.396346343833828</v>
+        <v>5.390689550325931</v>
       </c>
       <c r="O4" t="n">
-        <v>2.323003733064979</v>
+        <v>2.321785853675125</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1260913380476</v>
+        <v>368.1215989428234</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32307,28 +32356,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2237614130041332</v>
+        <v>-0.2243235257092967</v>
       </c>
       <c r="J5" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.378341203679189</v>
+        <v>0.3800686409440616</v>
       </c>
       <c r="M5" t="n">
-        <v>1.683557653001177</v>
+        <v>1.683282421961945</v>
       </c>
       <c r="N5" t="n">
-        <v>4.374193215001391</v>
+        <v>4.372223773631327</v>
       </c>
       <c r="O5" t="n">
-        <v>2.091457198940823</v>
+        <v>2.090986315983758</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1713275229891</v>
+        <v>368.1772607941858</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32389,28 +32438,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2547261020164821</v>
+        <v>-0.2552699747298974</v>
       </c>
       <c r="J6" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3778023569155489</v>
+        <v>0.3794252177426618</v>
       </c>
       <c r="M6" t="n">
-        <v>1.968718423941066</v>
+        <v>1.968699456088765</v>
       </c>
       <c r="N6" t="n">
-        <v>5.681587863021542</v>
+        <v>5.677257224630038</v>
       </c>
       <c r="O6" t="n">
-        <v>2.383608160546012</v>
+        <v>2.382699566590391</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1477450807234</v>
+        <v>371.1534858232391</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32471,28 +32520,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1267769917996452</v>
+        <v>-0.1265892959140585</v>
       </c>
       <c r="J7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08396938649182295</v>
+        <v>0.08400144021254718</v>
       </c>
       <c r="M7" t="n">
-        <v>2.423577308304087</v>
+        <v>2.420784403175818</v>
       </c>
       <c r="N7" t="n">
-        <v>9.322427653876231</v>
+        <v>9.308360545728439</v>
       </c>
       <c r="O7" t="n">
-        <v>3.053265080839892</v>
+        <v>3.050960593932416</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5716170831773</v>
+        <v>371.5696358958078</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32553,28 +32602,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1204923816829739</v>
+        <v>-0.1213648841458825</v>
       </c>
       <c r="J8" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K8" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1089628714164752</v>
+        <v>0.1105262771517624</v>
       </c>
       <c r="M8" t="n">
-        <v>1.828252981356397</v>
+        <v>1.829708009301852</v>
       </c>
       <c r="N8" t="n">
-        <v>6.312415364658253</v>
+        <v>6.314294610456693</v>
       </c>
       <c r="O8" t="n">
-        <v>2.512452062161237</v>
+        <v>2.512826020729786</v>
       </c>
       <c r="P8" t="n">
-        <v>373.3609747523084</v>
+        <v>373.3701842821493</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32635,28 +32684,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.131461939384212</v>
+        <v>-0.1318651040511285</v>
       </c>
       <c r="J9" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K9" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09631616599553849</v>
+        <v>0.09712609828458552</v>
       </c>
       <c r="M9" t="n">
-        <v>2.382423502259337</v>
+        <v>2.380770961939204</v>
       </c>
       <c r="N9" t="n">
-        <v>8.621374793836541</v>
+        <v>8.610375464891453</v>
       </c>
       <c r="O9" t="n">
-        <v>2.93621777016565</v>
+        <v>2.934344128573104</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1404059070097</v>
+        <v>368.1446614331412</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32717,28 +32766,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.196073681433445</v>
+        <v>-0.1975430397350499</v>
       </c>
       <c r="J10" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K10" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1410452181320606</v>
+        <v>0.1429564961211792</v>
       </c>
       <c r="M10" t="n">
-        <v>2.779574874228032</v>
+        <v>2.78281731922818</v>
       </c>
       <c r="N10" t="n">
-        <v>12.44828922265273</v>
+        <v>12.46216813569436</v>
       </c>
       <c r="O10" t="n">
-        <v>3.528213318756779</v>
+        <v>3.530179618049818</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9317438293558</v>
+        <v>364.9472533547736</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32780,7 +32829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K638"/>
+  <dimension ref="A1:K639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69125,6 +69174,63 @@
         </is>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.622087893955914,174.76590138471528</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.621786849288824,174.76671790780043</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.6214510224992,174.76750585908766</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.62103938453463,174.76823972222078</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.620581756941775,174.76893236086437</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.620054515033225,174.76953442922</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-36.61953206685932,174.77013490857095</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>-36.618932290611106,174.77062221093036</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>-36.61834538224041,174.77115383705953</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K639"/>
+  <dimension ref="A1:K642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25355,6 +25355,123 @@
       <c r="K639" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>364.57</v>
+      </c>
+      <c r="C640" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="D640" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="E640" t="n">
+        <v>360.46</v>
+      </c>
+      <c r="F640" t="n">
+        <v>362.08</v>
+      </c>
+      <c r="G640" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="H640" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="I640" t="n">
+        <v>362.23</v>
+      </c>
+      <c r="J640" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="C641" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="D641" t="n">
+        <v>364.18</v>
+      </c>
+      <c r="E641" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="F641" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="G641" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="H641" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="I641" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="J641" t="n">
+        <v>352.45</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="C642" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="D642" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="E642" t="n">
+        <v>360.85</v>
+      </c>
+      <c r="F642" t="n">
+        <v>362.68</v>
+      </c>
+      <c r="G642" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="H642" t="n">
+        <v>366.91</v>
+      </c>
+      <c r="I642" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="J642" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25369,7 +25486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B657"/>
+  <dimension ref="A1:B660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31942,6 +32059,36 @@
       </c>
       <c r="B657" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -32110,28 +32257,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2740644447735591</v>
+        <v>-0.2738697148499717</v>
       </c>
       <c r="J2" t="n">
+        <v>641</v>
+      </c>
+      <c r="K2" t="n">
         <v>638</v>
       </c>
-      <c r="K2" t="n">
-        <v>635</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2907174275007122</v>
+        <v>0.2925482407168246</v>
       </c>
       <c r="M2" t="n">
-        <v>2.57667756320093</v>
+        <v>2.565590531528766</v>
       </c>
       <c r="N2" t="n">
-        <v>9.800465163077305</v>
+        <v>9.754692747720824</v>
       </c>
       <c r="O2" t="n">
-        <v>3.130569463065355</v>
+        <v>3.123250349831218</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3752682607205</v>
+        <v>371.3732087146486</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32192,28 +32339,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2118715907308826</v>
+        <v>-0.2113032413798784</v>
       </c>
       <c r="J3" t="n">
+        <v>641</v>
+      </c>
+      <c r="K3" t="n">
         <v>638</v>
       </c>
-      <c r="K3" t="n">
-        <v>635</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.247392343130342</v>
+        <v>0.2482698243756194</v>
       </c>
       <c r="M3" t="n">
-        <v>2.268947297686434</v>
+        <v>2.261307887934705</v>
       </c>
       <c r="N3" t="n">
-        <v>7.303329695773823</v>
+        <v>7.270706277503302</v>
       </c>
       <c r="O3" t="n">
-        <v>2.702467334820871</v>
+        <v>2.696424721275063</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5589134972913</v>
+        <v>366.5529006230191</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32274,28 +32421,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1866513768508461</v>
+        <v>-0.1856410149620605</v>
       </c>
       <c r="J4" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K4" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.256097466155993</v>
+        <v>0.2558103134827929</v>
       </c>
       <c r="M4" t="n">
-        <v>1.881439949222615</v>
+        <v>1.877632591253849</v>
       </c>
       <c r="N4" t="n">
-        <v>5.390689550325931</v>
+        <v>5.370756030148244</v>
       </c>
       <c r="O4" t="n">
-        <v>2.321785853675125</v>
+        <v>2.317489165055199</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1215989428234</v>
+        <v>368.110896893235</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32356,28 +32503,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2243235257092967</v>
+        <v>-0.2259172951166086</v>
       </c>
       <c r="J5" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3800686409440616</v>
+        <v>0.3851345627106961</v>
       </c>
       <c r="M5" t="n">
-        <v>1.683282421961945</v>
+        <v>1.682020113432871</v>
       </c>
       <c r="N5" t="n">
-        <v>4.372223773631327</v>
+        <v>4.365042786237304</v>
       </c>
       <c r="O5" t="n">
-        <v>2.090986315983758</v>
+        <v>2.089268481128575</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1772607941858</v>
+        <v>368.1941417816683</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32438,28 +32585,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2552699747298974</v>
+        <v>-0.2572905818915786</v>
       </c>
       <c r="J6" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K6" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3794252177426618</v>
+        <v>0.3846941954260432</v>
       </c>
       <c r="M6" t="n">
-        <v>1.968699456088765</v>
+        <v>1.970794978300025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.677257224630038</v>
+        <v>5.672116161401178</v>
       </c>
       <c r="O6" t="n">
-        <v>2.382699566590391</v>
+        <v>2.381620490632623</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1534858232391</v>
+        <v>371.1748876194503</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32520,28 +32667,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1265892959140585</v>
+        <v>-0.1260413291819851</v>
       </c>
       <c r="J7" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K7" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08400144021254718</v>
+        <v>0.08411621960923654</v>
       </c>
       <c r="M7" t="n">
-        <v>2.420784403175818</v>
+        <v>2.412357315037668</v>
       </c>
       <c r="N7" t="n">
-        <v>9.308360545728439</v>
+        <v>9.266346374083144</v>
       </c>
       <c r="O7" t="n">
-        <v>3.050960593932416</v>
+        <v>3.044067406297558</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5696358958078</v>
+        <v>371.5638318367874</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32602,28 +32749,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1213648841458825</v>
+        <v>-0.1246568974846181</v>
       </c>
       <c r="J8" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1105262771517624</v>
+        <v>0.1160491575826399</v>
       </c>
       <c r="M8" t="n">
-        <v>1.829708009301852</v>
+        <v>1.837363177294903</v>
       </c>
       <c r="N8" t="n">
-        <v>6.314294610456693</v>
+        <v>6.340751143378115</v>
       </c>
       <c r="O8" t="n">
-        <v>2.512826020729786</v>
+        <v>2.518084816557638</v>
       </c>
       <c r="P8" t="n">
-        <v>373.3701842821493</v>
+        <v>373.4050535576621</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32684,28 +32831,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1318651040511285</v>
+        <v>-0.1346338638760749</v>
       </c>
       <c r="J9" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K9" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09712609828458552</v>
+        <v>0.1013450471723741</v>
       </c>
       <c r="M9" t="n">
-        <v>2.380770961939204</v>
+        <v>2.383835718674718</v>
       </c>
       <c r="N9" t="n">
-        <v>8.610375464891453</v>
+        <v>8.610354296057452</v>
       </c>
       <c r="O9" t="n">
-        <v>2.934344128573104</v>
+        <v>2.934340521489871</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1446614331412</v>
+        <v>368.1739901431711</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32766,28 +32913,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1975430397350499</v>
+        <v>-0.2037994739887646</v>
       </c>
       <c r="J10" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K10" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1429564961211792</v>
+        <v>0.1500023379079644</v>
       </c>
       <c r="M10" t="n">
-        <v>2.78281731922818</v>
+        <v>2.802582568172409</v>
       </c>
       <c r="N10" t="n">
-        <v>12.46216813569436</v>
+        <v>12.60804586585476</v>
       </c>
       <c r="O10" t="n">
-        <v>3.530179618049818</v>
+        <v>3.550781021952037</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9472533547736</v>
+        <v>365.0135258505327</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32829,7 +32976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K639"/>
+  <dimension ref="A1:K642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69231,6 +69378,177 @@
         </is>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.62208910138819,174.76590213889014</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.62179639160677,174.76672398034225</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.621453286837216,174.7675076918651</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.621039806856416,174.76824014115294</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.62058622670281,174.7689372292948</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.62005445307648,174.7695343480289</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-36.6195363682801,174.77014250028492</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>-36.61893755789134,174.77063379990423</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>-36.618349941284464,174.77116386779508</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.62209127476628,174.76590349640492</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.62179711329466,174.76672443961021</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.62145381518274,174.76750811951317</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.62104008840427,174.76824042044106</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.620586091255525,174.7689370817666</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.62005470090348,174.76953467279313</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-36.61953678287486,174.77014323201644</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>-36.61894193991349,174.7706434411526</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>-36.618357333130724,174.7711801312231</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.622092079721114,174.7659039991882</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.621798235920274,174.766725154027</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.62145230562409,174.76750689766152</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.62103706176481,174.76823741809395</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.62058216328369,174.76893280344893</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.620054762860235,174.76953475398417</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-36.61953486537411,174.77013984775823</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>-36.61893968250824,174.77063847444876</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>-36.61835578394158,174.77117672271999</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K642"/>
+  <dimension ref="A1:K644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25470,6 +25470,84 @@
         <v>352.8</v>
       </c>
       <c r="K642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="C643" t="n">
+        <v>360.57</v>
+      </c>
+      <c r="D643" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="E643" t="n">
+        <v>360.89</v>
+      </c>
+      <c r="F643" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="G643" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="H643" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="I643" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="J643" t="n">
+        <v>354.46</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="C644" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="D644" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="E644" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="F644" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="G644" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="H644" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="I644" t="n">
+        <v>362.99</v>
+      </c>
+      <c r="J644" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="K644" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25486,7 +25564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B660"/>
+  <dimension ref="A1:B662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32089,6 +32167,26 @@
       </c>
       <c r="B660" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -32257,34 +32355,30 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2738697148499717</v>
+        <v>-0.2747681395493347</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K2" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2925482407168246</v>
+        <v>0.2951959231226536</v>
       </c>
       <c r="M2" t="n">
-        <v>2.565590531528766</v>
+        <v>2.561742652310982</v>
       </c>
       <c r="N2" t="n">
-        <v>9.754692747720824</v>
+        <v>9.730650438563913</v>
       </c>
       <c r="O2" t="n">
-        <v>3.123250349831218</v>
+        <v>3.11939905086924</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3732087146486</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>371.382749593166</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.76773520699282 -36.62502370861356, 174.76310850191334 -36.6176161911201)</t>
@@ -32339,34 +32433,30 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2113032413798784</v>
+        <v>-0.2114212857710518</v>
       </c>
       <c r="J3" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K3" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2482698243756194</v>
+        <v>0.2497572823393822</v>
       </c>
       <c r="M3" t="n">
-        <v>2.261307887934705</v>
+        <v>2.254856293279941</v>
       </c>
       <c r="N3" t="n">
-        <v>7.270706277503302</v>
+        <v>7.24823258271532</v>
       </c>
       <c r="O3" t="n">
-        <v>2.696424721275063</v>
+        <v>2.692254182412077</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5529006230191</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>366.5541533655969</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.76856969590492 -36.624696597864045, 174.76387379415723 -36.61731733893218)</t>
@@ -32421,34 +32511,30 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1856410149620605</v>
+        <v>-0.185447897066429</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2558103134827929</v>
+        <v>0.2567121158669399</v>
       </c>
       <c r="M4" t="n">
-        <v>1.877632591253849</v>
+        <v>1.872736897120266</v>
       </c>
       <c r="N4" t="n">
-        <v>5.370756030148244</v>
+        <v>5.354427124092826</v>
       </c>
       <c r="O4" t="n">
-        <v>2.317489165055199</v>
+        <v>2.313963509671841</v>
       </c>
       <c r="P4" t="n">
-        <v>368.110896893235</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.1088433687807</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.76973306944018 -36.624202547019, 174.76411038047095 -36.61725573135326)</t>
@@ -32503,34 +32589,30 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2259172951166086</v>
+        <v>-0.2265339294313389</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3851345627106961</v>
+        <v>0.3878766450568734</v>
       </c>
       <c r="M5" t="n">
-        <v>1.682020113432871</v>
+        <v>1.679333885188053</v>
       </c>
       <c r="N5" t="n">
-        <v>4.365042786237304</v>
+        <v>4.354821262308663</v>
       </c>
       <c r="O5" t="n">
-        <v>2.089268481128575</v>
+        <v>2.086820850554417</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1941417816683</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.2006956508711</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.77075702916272 -36.623576946003425, 174.7643300207159 -36.61709777625188)</t>
@@ -32585,34 +32667,30 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2572905818915786</v>
+        <v>-0.2581236261605753</v>
       </c>
       <c r="J6" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3846941954260432</v>
+        <v>0.38760283010923</v>
       </c>
       <c r="M6" t="n">
-        <v>1.970794978300025</v>
+        <v>1.969289494011812</v>
       </c>
       <c r="N6" t="n">
-        <v>5.672116161401178</v>
+        <v>5.660571095176864</v>
       </c>
       <c r="O6" t="n">
-        <v>2.381620490632623</v>
+        <v>2.379195472250413</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1748876194503</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>371.1837416234019</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.77160816489436 -36.62303833192341, 174.76481781117982 -36.61680387913344)</t>
@@ -32667,34 +32745,30 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1260413291819851</v>
+        <v>-0.1256116912070352</v>
       </c>
       <c r="J7" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08411621960923654</v>
+        <v>0.08410050880102427</v>
       </c>
       <c r="M7" t="n">
-        <v>2.412357315037668</v>
+        <v>2.40711296411745</v>
       </c>
       <c r="N7" t="n">
-        <v>9.266346374083144</v>
+        <v>9.239911659701075</v>
       </c>
       <c r="O7" t="n">
-        <v>3.044067406297558</v>
+        <v>3.039722299767049</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5638318367874</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>371.5592626255564</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.77252908697537 -36.622339625450486, 174.76505397115486 -36.616635243740426)</t>
@@ -32749,34 +32823,30 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1246568974846181</v>
+        <v>-0.1263731043279344</v>
       </c>
       <c r="J8" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K8" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1160491575826399</v>
+        <v>0.1192214807803696</v>
       </c>
       <c r="M8" t="n">
-        <v>1.837363177294903</v>
+        <v>1.840083911875033</v>
       </c>
       <c r="N8" t="n">
-        <v>6.340751143378115</v>
+        <v>6.344245925302155</v>
       </c>
       <c r="O8" t="n">
-        <v>2.518084816557638</v>
+        <v>2.518778657465192</v>
       </c>
       <c r="P8" t="n">
-        <v>373.4050535576621</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>373.423296607961</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.77349592419137 -36.621436302644454, 174.76507292343683 -36.616663756981545)</t>
@@ -32831,34 +32901,30 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1346338638760749</v>
+        <v>-0.1358977403617216</v>
       </c>
       <c r="J9" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K9" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1013450471723741</v>
+        <v>0.1035580747376907</v>
       </c>
       <c r="M9" t="n">
-        <v>2.383835718674718</v>
+        <v>2.382870276305345</v>
       </c>
       <c r="N9" t="n">
-        <v>8.610354296057452</v>
+        <v>8.596489988757776</v>
       </c>
       <c r="O9" t="n">
-        <v>2.934340521489871</v>
+        <v>2.931977146697732</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1739901431711</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.1874243840953</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.7741614969706 -36.62054083682528, 174.76519208527463 -36.61646404905145)</t>
@@ -32913,34 +32979,30 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2037994739887646</v>
+        <v>-0.2062585313939148</v>
       </c>
       <c r="J10" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K10" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1500023379079644</v>
+        <v>0.1534443415431389</v>
       </c>
       <c r="M10" t="n">
-        <v>2.802582568172409</v>
+        <v>2.80678404072237</v>
       </c>
       <c r="N10" t="n">
-        <v>12.60804586585476</v>
+        <v>12.62080277581966</v>
       </c>
       <c r="O10" t="n">
-        <v>3.550781021952037</v>
+        <v>3.55257692046487</v>
       </c>
       <c r="P10" t="n">
-        <v>365.0135258505327</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>365.0396624169012</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.77461256174013 -36.61991731501647, 174.76564318375566 -36.615840536611145)</t>
@@ -32976,7 +33038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K642"/>
+  <dimension ref="A1:K644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69549,6 +69611,120 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.62210254413384,174.76591053537175</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.621805292424,174.76672964464737</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.62146015532899,174.76751325129064</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.62103678021695,174.76823713880583</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.62058284052023,174.76893354108987</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.620057427000496,174.76953824519944</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-36.61953398436021,174.77013829282888</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>-36.61893764641705,174.7706339946769</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>-36.6183484363574,174.77116055667835</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.622105763953044,174.7659125465055</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.621802004734796,174.76672755242643</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.621457664557276,174.76751123523513</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.62103185312925,174.7682322512645</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.62057654222028,174.76892668102963</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.620050611757755,174.7695293141841</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-36.619530874899255,174.77013280484314</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>-36.61893419391419,174.7706263985426</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>-36.61833737071426,174.77113621023582</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K644"/>
+  <dimension ref="A1:K647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25550,6 +25550,123 @@
       <c r="K644" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="C645" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="D645" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="E645" t="n">
+        <v>361.87</v>
+      </c>
+      <c r="F645" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="G645" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="H645" t="n">
+        <v>368.02</v>
+      </c>
+      <c r="I645" t="n">
+        <v>363.64</v>
+      </c>
+      <c r="J645" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="C646" t="n">
+        <v>360.05</v>
+      </c>
+      <c r="D646" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="E646" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="F646" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="G646" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="H646" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="I646" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="J646" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="C647" t="n">
+        <v>360.03</v>
+      </c>
+      <c r="D647" t="n">
+        <v>363.26</v>
+      </c>
+      <c r="E647" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="F647" t="n">
+        <v>364.4</v>
+      </c>
+      <c r="G647" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="H647" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="I647" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="J647" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25564,7 +25681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B662"/>
+  <dimension ref="A1:B665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32187,6 +32304,36 @@
       </c>
       <c r="B662" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -32355,28 +32502,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2747681395493347</v>
+        <v>-0.2761614281715123</v>
       </c>
       <c r="J2" t="n">
+        <v>646</v>
+      </c>
+      <c r="K2" t="n">
         <v>643</v>
       </c>
-      <c r="K2" t="n">
-        <v>640</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2951959231226536</v>
+        <v>0.2992424446885967</v>
       </c>
       <c r="M2" t="n">
-        <v>2.561742652310982</v>
+        <v>2.556244227964243</v>
       </c>
       <c r="N2" t="n">
-        <v>9.730650438563913</v>
+        <v>9.695468869874611</v>
       </c>
       <c r="O2" t="n">
-        <v>3.11939905086924</v>
+        <v>3.113754786407338</v>
       </c>
       <c r="P2" t="n">
-        <v>371.382749593166</v>
+        <v>371.3976034043141</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32433,28 +32580,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2114212857710518</v>
+        <v>-0.2119898249355115</v>
       </c>
       <c r="J3" t="n">
+        <v>646</v>
+      </c>
+      <c r="K3" t="n">
         <v>643</v>
       </c>
-      <c r="K3" t="n">
-        <v>640</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2497572823393822</v>
+        <v>0.2526419426755395</v>
       </c>
       <c r="M3" t="n">
-        <v>2.254856293279941</v>
+        <v>2.246924391951039</v>
       </c>
       <c r="N3" t="n">
-        <v>7.24823258271532</v>
+        <v>7.216913214467096</v>
       </c>
       <c r="O3" t="n">
-        <v>2.692254182412077</v>
+        <v>2.686431315791844</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5541533655969</v>
+        <v>366.5602187475401</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32511,28 +32658,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.185447897066429</v>
+        <v>-0.1853534367506121</v>
       </c>
       <c r="J4" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2567121158669399</v>
+        <v>0.2584760161587855</v>
       </c>
       <c r="M4" t="n">
-        <v>1.872736897120266</v>
+        <v>1.865283566809208</v>
       </c>
       <c r="N4" t="n">
-        <v>5.354427124092826</v>
+        <v>5.330025957858331</v>
       </c>
       <c r="O4" t="n">
-        <v>2.313963509671841</v>
+        <v>2.308684897914467</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1088433687807</v>
+        <v>368.1078376070635</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32589,28 +32736,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2265339294313389</v>
+        <v>-0.226899637832283</v>
       </c>
       <c r="J5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3878766450568734</v>
+        <v>0.3910610489451161</v>
       </c>
       <c r="M5" t="n">
-        <v>1.679333885188053</v>
+        <v>1.673025357174528</v>
       </c>
       <c r="N5" t="n">
-        <v>4.354821262308663</v>
+        <v>4.33530729401384</v>
       </c>
       <c r="O5" t="n">
-        <v>2.086820850554417</v>
+        <v>2.082140075502568</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2006956508711</v>
+        <v>368.204598843598</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32667,28 +32814,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2581236261605753</v>
+        <v>-0.2584202502192657</v>
       </c>
       <c r="J6" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K6" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38760283010923</v>
+        <v>0.390564668281411</v>
       </c>
       <c r="M6" t="n">
-        <v>1.969289494011812</v>
+        <v>1.962047859746397</v>
       </c>
       <c r="N6" t="n">
-        <v>5.660571095176864</v>
+        <v>5.635219641421378</v>
       </c>
       <c r="O6" t="n">
-        <v>2.379195472250413</v>
+        <v>2.373861757015639</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1837416234019</v>
+        <v>371.1869057222911</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32745,28 +32892,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1256116912070352</v>
+        <v>-0.1237234055108135</v>
       </c>
       <c r="J7" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K7" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08410050880102427</v>
+        <v>0.08242078616796267</v>
       </c>
       <c r="M7" t="n">
-        <v>2.40711296411745</v>
+        <v>2.405755553303043</v>
       </c>
       <c r="N7" t="n">
-        <v>9.239911659701075</v>
+        <v>9.215812543895415</v>
       </c>
       <c r="O7" t="n">
-        <v>3.039722299767049</v>
+        <v>3.03575567921653</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5592626255564</v>
+        <v>371.5391101965689</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32823,28 +32970,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1263731043279344</v>
+        <v>-0.1285526696092087</v>
       </c>
       <c r="J8" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K8" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1192214807803696</v>
+        <v>0.1235503610483322</v>
       </c>
       <c r="M8" t="n">
-        <v>1.840083911875033</v>
+        <v>1.842137413085427</v>
       </c>
       <c r="N8" t="n">
-        <v>6.344245925302155</v>
+        <v>6.339693100871348</v>
       </c>
       <c r="O8" t="n">
-        <v>2.518778657465192</v>
+        <v>2.517874719057989</v>
       </c>
       <c r="P8" t="n">
-        <v>373.423296607961</v>
+        <v>373.4465584207465</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32901,28 +33048,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1358977403617216</v>
+        <v>-0.1368294401474725</v>
       </c>
       <c r="J9" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K9" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1035580747376907</v>
+        <v>0.105755118494546</v>
       </c>
       <c r="M9" t="n">
-        <v>2.382870276305345</v>
+        <v>2.376508550857582</v>
       </c>
       <c r="N9" t="n">
-        <v>8.596489988757776</v>
+        <v>8.561251473328728</v>
       </c>
       <c r="O9" t="n">
-        <v>2.931977146697732</v>
+        <v>2.925961632237977</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1874243840953</v>
+        <v>368.1973669508271</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32979,28 +33126,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2062585313939148</v>
+        <v>-0.2084853152476955</v>
       </c>
       <c r="J10" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K10" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1534443415431389</v>
+        <v>0.1573404663649693</v>
       </c>
       <c r="M10" t="n">
-        <v>2.80678404072237</v>
+        <v>2.805654332728345</v>
       </c>
       <c r="N10" t="n">
-        <v>12.62080277581966</v>
+        <v>12.58884058489007</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55257692046487</v>
+        <v>3.548075617132486</v>
       </c>
       <c r="P10" t="n">
-        <v>365.0396624169012</v>
+        <v>365.0634311248065</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33038,7 +33185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K644"/>
+  <dimension ref="A1:K647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69725,6 +69872,177 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.62210447602537,174.76591174205197</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.621802405672504,174.7667278075753</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.621457664557276,174.76751123523513</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.621029882294124,174.76823029624813</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.62057308831367,174.76892291906157</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.620045717173866,174.76952290009226</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-36.61952911287125,174.77012969498472</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>-36.618931316828075,174.77062006843113</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>-36.618334139545475,174.77112910107587</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.62210415404344,174.76591154093856</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.62180946217613,174.7667322981962</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.621463249924076,174.7675157560871</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.62103086771169,174.76823127375633</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.62057572953638,174.7689257958606</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.620047575876654,174.76952533582323</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-36.61953154861582,174.77013399390665</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>-36.618932644714015,174.770622990021</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>-36.61833613136189,174.77113348343465</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.622106166430456,174.76591279789722</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.62180962255121,174.76673240025576</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.621460759152406,174.7675137400314</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.62103044538987,174.76823085482425</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.620570514814546,174.76892011602675</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.62004410629808,174.7695207891255</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.619530926723606,174.77013289630955</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-36.61893069714795,174.77061870502257</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>-36.61833878711686,174.77113932658008</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K647"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25665,6 +25665,45 @@
         <v>356.64</v>
       </c>
       <c r="K647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>362.72</v>
+      </c>
+      <c r="C648" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="D648" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="E648" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="F648" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="G648" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="H648" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="I648" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="J648" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="K648" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25681,7 +25720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B665"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32334,6 +32373,16 @@
       </c>
       <c r="B665" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -32502,28 +32551,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2761614281715123</v>
+        <v>-0.2765768093690072</v>
       </c>
       <c r="J2" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K2" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2992424446885967</v>
+        <v>0.3005329115392333</v>
       </c>
       <c r="M2" t="n">
-        <v>2.556244227964243</v>
+        <v>2.55419025813307</v>
       </c>
       <c r="N2" t="n">
-        <v>9.695468869874611</v>
+        <v>9.68315058708672</v>
       </c>
       <c r="O2" t="n">
-        <v>3.113754786407338</v>
+        <v>3.111776114550454</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3976034043141</v>
+        <v>371.4020408522057</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32580,28 +32629,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2119898249355115</v>
+        <v>-0.2122508282808925</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K3" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2526419426755395</v>
+        <v>0.2537261449898816</v>
       </c>
       <c r="M3" t="n">
-        <v>2.246924391951039</v>
+        <v>2.244618301133827</v>
       </c>
       <c r="N3" t="n">
-        <v>7.216913214467096</v>
+        <v>7.206787366485576</v>
       </c>
       <c r="O3" t="n">
-        <v>2.686431315791844</v>
+        <v>2.684546026144007</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5602187475401</v>
+        <v>366.5630070026457</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32658,28 +32707,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1853534367506121</v>
+        <v>-0.1853735115583734</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2584760161587855</v>
+        <v>0.259175186027353</v>
       </c>
       <c r="M4" t="n">
-        <v>1.865283566809208</v>
+        <v>1.862500961738507</v>
       </c>
       <c r="N4" t="n">
-        <v>5.330025957858331</v>
+        <v>5.321794252344775</v>
       </c>
       <c r="O4" t="n">
-        <v>2.308684897914467</v>
+        <v>2.306901439668538</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1078376070635</v>
+        <v>368.1080522895948</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32736,28 +32785,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.226899637832283</v>
+        <v>-0.2270470409253794</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K5" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3910610489451161</v>
+        <v>0.3921686686182547</v>
       </c>
       <c r="M5" t="n">
-        <v>1.673025357174528</v>
+        <v>1.67103637362977</v>
       </c>
       <c r="N5" t="n">
-        <v>4.33530729401384</v>
+        <v>4.328949362084179</v>
       </c>
       <c r="O5" t="n">
-        <v>2.082140075502568</v>
+        <v>2.080612737172437</v>
       </c>
       <c r="P5" t="n">
-        <v>368.204598843598</v>
+        <v>368.2061751909056</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32814,28 +32863,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2584202502192657</v>
+        <v>-0.2584679176693289</v>
       </c>
       <c r="J6" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K6" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.390564668281411</v>
+        <v>0.3914675692547219</v>
       </c>
       <c r="M6" t="n">
-        <v>1.962047859746397</v>
+        <v>1.959281950007157</v>
       </c>
       <c r="N6" t="n">
-        <v>5.635219641421378</v>
+        <v>5.626545711643368</v>
       </c>
       <c r="O6" t="n">
-        <v>2.373861757015639</v>
+        <v>2.372034087369608</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1869057222911</v>
+        <v>371.1874154840267</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32892,28 +32941,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1237234055108135</v>
+        <v>-0.123151125156078</v>
       </c>
       <c r="J7" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K7" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08242078616796267</v>
+        <v>0.08193773006629024</v>
       </c>
       <c r="M7" t="n">
-        <v>2.405755553303043</v>
+        <v>2.405000701929744</v>
       </c>
       <c r="N7" t="n">
-        <v>9.215812543895415</v>
+        <v>9.206734167144765</v>
       </c>
       <c r="O7" t="n">
-        <v>3.03575567921653</v>
+        <v>3.034260069134609</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5391101965689</v>
+        <v>371.5329901581259</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32970,28 +33019,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1285526696092087</v>
+        <v>-0.1293539947529117</v>
       </c>
       <c r="J8" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K8" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1235503610483322</v>
+        <v>0.1251026804743136</v>
       </c>
       <c r="M8" t="n">
-        <v>1.842137413085427</v>
+        <v>1.843162655520542</v>
       </c>
       <c r="N8" t="n">
-        <v>6.339693100871348</v>
+        <v>6.340022308870172</v>
       </c>
       <c r="O8" t="n">
-        <v>2.517874719057989</v>
+        <v>2.517940092391035</v>
       </c>
       <c r="P8" t="n">
-        <v>373.4465584207465</v>
+        <v>373.4551278931112</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33048,28 +33097,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1368294401474725</v>
+        <v>-0.1371510024811048</v>
       </c>
       <c r="J9" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K9" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L9" t="n">
-        <v>0.105755118494546</v>
+        <v>0.1065077134428226</v>
       </c>
       <c r="M9" t="n">
-        <v>2.376508550857582</v>
+        <v>2.37444916305906</v>
       </c>
       <c r="N9" t="n">
-        <v>8.561251473328728</v>
+        <v>8.549650148613742</v>
       </c>
       <c r="O9" t="n">
-        <v>2.925961632237977</v>
+        <v>2.923978479505918</v>
       </c>
       <c r="P9" t="n">
-        <v>368.1973669508271</v>
+        <v>368.2008057790646</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33126,28 +33175,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2084853152476955</v>
+        <v>-0.2092511871946242</v>
       </c>
       <c r="J10" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K10" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1573404663649693</v>
+        <v>0.1586744667032014</v>
       </c>
       <c r="M10" t="n">
-        <v>2.805654332728345</v>
+        <v>2.805436557595425</v>
       </c>
       <c r="N10" t="n">
-        <v>12.58884058489007</v>
+        <v>12.57863479291164</v>
       </c>
       <c r="O10" t="n">
-        <v>3.548075617132486</v>
+        <v>3.546637110406369</v>
       </c>
       <c r="P10" t="n">
-        <v>365.0634311248065</v>
+        <v>365.0716214562041</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33185,7 +33234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K647"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70043,6 +70092,63 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.62210399305249,174.7659114403819</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.62180914142597,174.76673209407704</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.62146181584344,174.76751459532773</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.62103107887259,174.76823148322237</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.620572140182425,174.76892188636452</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.6200467704388,174.76952428033982</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.61953201503497,174.77013481710452</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-36.6189318037196,174.77062113968074</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>-36.61833688382583,174.7711351389925</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25704,6 +25704,240 @@
         <v>357.07</v>
       </c>
       <c r="K648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="C649" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="D649" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="E649" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="F649" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="G649" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="H649" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="I649" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="J649" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="C650" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="D650" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="E650" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="F650" t="n">
+        <v>365.09</v>
+      </c>
+      <c r="G650" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="H650" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="I650" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="J650" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="C651" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="D651" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="E651" t="n">
+        <v>362.77</v>
+      </c>
+      <c r="F651" t="n">
+        <v>364.84</v>
+      </c>
+      <c r="G651" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="H651" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="I651" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="J651" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="C652" t="n">
+        <v>360.35</v>
+      </c>
+      <c r="D652" t="n">
+        <v>363.91</v>
+      </c>
+      <c r="E652" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="F652" t="n">
+        <v>365.72</v>
+      </c>
+      <c r="G652" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="H652" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="I652" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="J652" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="C653" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="D653" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="E653" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="F653" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="G653" t="n">
+        <v>366.73</v>
+      </c>
+      <c r="H653" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="I653" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="J653" t="n">
+        <v>355.94</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="C654" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="D654" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="E654" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="F654" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="G654" t="n">
+        <v>366.53</v>
+      </c>
+      <c r="H654" t="n">
+        <v>368.31</v>
+      </c>
+      <c r="I654" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="J654" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="K654" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25720,7 +25954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32383,6 +32617,66 @@
       </c>
       <c r="B666" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -32551,28 +32845,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2765768093690072</v>
+        <v>-0.2769191803920124</v>
       </c>
       <c r="J2" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K2" t="n">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3005329115392333</v>
+        <v>0.3052804022985848</v>
       </c>
       <c r="M2" t="n">
-        <v>2.55419025813307</v>
+        <v>2.536719659375123</v>
       </c>
       <c r="N2" t="n">
-        <v>9.68315058708672</v>
+        <v>9.59832997395597</v>
       </c>
       <c r="O2" t="n">
-        <v>3.111776114550454</v>
+        <v>3.098117165950308</v>
       </c>
       <c r="P2" t="n">
-        <v>371.4020408522057</v>
+        <v>371.4056982667348</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32629,28 +32923,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2122508282808925</v>
+        <v>-0.2137035916510803</v>
       </c>
       <c r="J3" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K3" t="n">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2537261449898816</v>
+        <v>0.2600828587289626</v>
       </c>
       <c r="M3" t="n">
-        <v>2.244618301133827</v>
+        <v>2.230446817647885</v>
       </c>
       <c r="N3" t="n">
-        <v>7.206787366485576</v>
+        <v>7.146180426789315</v>
       </c>
       <c r="O3" t="n">
-        <v>2.684546026144007</v>
+        <v>2.673234076318292</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5630070026457</v>
+        <v>366.5785989410201</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32707,28 +33001,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1853735115583734</v>
+        <v>-0.1845382497637851</v>
       </c>
       <c r="J4" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K4" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.259175186027353</v>
+        <v>0.2613045829401982</v>
       </c>
       <c r="M4" t="n">
-        <v>1.862500961738507</v>
+        <v>1.849399982214272</v>
       </c>
       <c r="N4" t="n">
-        <v>5.321794252344775</v>
+        <v>5.275157804751656</v>
       </c>
       <c r="O4" t="n">
-        <v>2.306901439668538</v>
+        <v>2.296771169435836</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1080522895948</v>
+        <v>368.0990762091721</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32785,28 +33079,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2270470409253794</v>
+        <v>-0.2254652105373951</v>
       </c>
       <c r="J5" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K5" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3921686686182547</v>
+        <v>0.393252473000263</v>
       </c>
       <c r="M5" t="n">
-        <v>1.67103637362977</v>
+        <v>1.664775055425664</v>
       </c>
       <c r="N5" t="n">
-        <v>4.328949362084179</v>
+        <v>4.297737786868209</v>
       </c>
       <c r="O5" t="n">
-        <v>2.080612737172437</v>
+        <v>2.073098595549235</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2061751909056</v>
+        <v>368.1891700864085</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32863,28 +33157,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2584679176693289</v>
+        <v>-0.2565082511315251</v>
       </c>
       <c r="J6" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K6" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3914675692547219</v>
+        <v>0.3922424363332764</v>
       </c>
       <c r="M6" t="n">
-        <v>1.959281950007157</v>
+        <v>1.94972053547568</v>
       </c>
       <c r="N6" t="n">
-        <v>5.626545711643368</v>
+        <v>5.586280740668021</v>
       </c>
       <c r="O6" t="n">
-        <v>2.372034087369608</v>
+        <v>2.363531413091017</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1874154840267</v>
+        <v>371.1663535327369</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32941,28 +33235,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.123151125156078</v>
+        <v>-0.1232822402895117</v>
       </c>
       <c r="J7" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K7" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08193773006629024</v>
+        <v>0.08348690452120155</v>
       </c>
       <c r="M7" t="n">
-        <v>2.405000701929744</v>
+        <v>2.396258892032613</v>
       </c>
       <c r="N7" t="n">
-        <v>9.206734167144765</v>
+        <v>9.142514020177195</v>
       </c>
       <c r="O7" t="n">
-        <v>3.034260069134609</v>
+        <v>3.023659044961451</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5329901581259</v>
+        <v>371.5344373695367</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33019,28 +33313,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1293539947529117</v>
+        <v>-0.1328462273058835</v>
       </c>
       <c r="J8" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K8" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1251026804743136</v>
+        <v>0.1328006841826372</v>
       </c>
       <c r="M8" t="n">
-        <v>1.843162655520542</v>
+        <v>1.842860321255929</v>
       </c>
       <c r="N8" t="n">
-        <v>6.340022308870172</v>
+        <v>6.31482541841549</v>
       </c>
       <c r="O8" t="n">
-        <v>2.517940092391035</v>
+        <v>2.512931638229638</v>
       </c>
       <c r="P8" t="n">
-        <v>373.4551278931112</v>
+        <v>373.4926407048645</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33097,28 +33391,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1371510024811048</v>
+        <v>-0.1383061830499163</v>
       </c>
       <c r="J9" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K9" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1065077134428226</v>
+        <v>0.1100596675417171</v>
       </c>
       <c r="M9" t="n">
-        <v>2.37444916305906</v>
+        <v>2.358312004986823</v>
       </c>
       <c r="N9" t="n">
-        <v>8.549650148613742</v>
+        <v>8.475399303407203</v>
       </c>
       <c r="O9" t="n">
-        <v>2.923978479505918</v>
+        <v>2.911253905692048</v>
       </c>
       <c r="P9" t="n">
-        <v>368.2008057790646</v>
+        <v>368.2132232896527</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33175,28 +33469,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2092511871946242</v>
+        <v>-0.2148617504278016</v>
       </c>
       <c r="J10" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="K10" t="n">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1586744667032014</v>
+        <v>0.1677596764280266</v>
       </c>
       <c r="M10" t="n">
-        <v>2.805436557595425</v>
+        <v>2.809533944109954</v>
       </c>
       <c r="N10" t="n">
-        <v>12.57863479291164</v>
+        <v>12.54942065629306</v>
       </c>
       <c r="O10" t="n">
-        <v>3.546637110406369</v>
+        <v>3.542516147640411</v>
       </c>
       <c r="P10" t="n">
-        <v>365.0716214562041</v>
+        <v>365.1319128781516</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33234,7 +33528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K648"/>
+  <dimension ref="A1:K654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70149,6 +70443,348 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.62210045125133,174.7659092281349</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.62180809898795,174.76673143068982</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.621458645770375,174.7675120294388</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.62102615178464,174.76822659568174</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.62056577415808,174.76891495254208</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.62004652261176,174.76952395557566</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.61952999388525,174.77013124991393</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-36.61892861679311,174.77061412786543</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>-36.61833723792651,174.77113591807853</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.622099807287476,174.76590882590816</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.6218088206758,174.7667318899579</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.6214587212483,174.7675120905314</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.621024814432175,174.7682252690637</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.62056584188173,174.76891502630613</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.62004943457938,174.76952777155435</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-36.61953030483138,174.77013179871244</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-36.61892914794755,174.77061529650126</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>-36.61833626414964,174.77113377559192</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.6221010147197,174.76590958008325</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.62181154705217,174.7667336249707</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.62145992889519,174.76751306801287</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.621023547466635,174.76822401226767</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.62056753497337,174.76891687040774</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.6200525943739,174.7695319122975</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-36.619530253007014,174.77013170724604</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>-36.61893003320495,174.7706172442277</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>-36.61833998220649,174.77114195599563</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.62209038931595,174.76590294334332</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.62180705654992,174.76673076730262</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.62145585308692,174.76750976901297</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.62101812766951,174.76821863597408</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.62056157529071,174.76891037917048</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.62006653464196,174.76955018028602</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-36.61952714354573,174.77012621926082</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-36.61892959057624,174.77061627036448</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>-36.61833878711686,174.77113932658008</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.622089664856595,174.7659024908384</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.62180841973811,174.76673163480896</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.62145592856485,174.76750983010558</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.621017705347654,174.76821821704218</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.62056055943567,174.76890927270966</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.620067525949786,174.76955147934322</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-36.61952688442395,174.7701257619287</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>-36.61893069714795,174.77061870502257</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>-36.61834188549727,174.77114614358354</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.62208902089272,174.7659020886118</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.621810183863985,174.7667327574643</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.62145947602761,174.76751270145732</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.621021013535554,174.76822149867576</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.620563132935075,174.76891207574374</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.62006876508457,174.7695531031648</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-36.61952760996495,174.77012704245857</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-36.618932644714015,174.770622990021</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>-36.61834405436333,174.7711509154863</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K654"/>
+  <dimension ref="A1:K658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25938,6 +25938,162 @@
         <v>355.45</v>
       </c>
       <c r="K654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="C655" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="D655" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="E655" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="F655" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="G655" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="H655" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="I655" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="J655" t="n">
+        <v>354.77</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="C656" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="D656" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="E656" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="F656" t="n">
+        <v>365.43</v>
+      </c>
+      <c r="G656" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="H656" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="I656" t="n">
+        <v>363.23</v>
+      </c>
+      <c r="J656" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="C657" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="D657" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="E657" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="F657" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="G657" t="n">
+        <v>366.92</v>
+      </c>
+      <c r="H657" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="I657" t="n">
+        <v>363.55</v>
+      </c>
+      <c r="J657" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="C658" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="D658" t="n">
+        <v>363.88</v>
+      </c>
+      <c r="E658" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="F658" t="n">
+        <v>365.08</v>
+      </c>
+      <c r="G658" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="H658" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="I658" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="J658" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="K658" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25954,7 +26110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32677,6 +32833,46 @@
       </c>
       <c r="B672" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -32845,28 +33041,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2769191803920124</v>
+        <v>-0.2754682561973847</v>
       </c>
       <c r="J2" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K2" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3052804022985848</v>
+        <v>0.3057105901769908</v>
       </c>
       <c r="M2" t="n">
-        <v>2.536719659375123</v>
+        <v>2.528899887711211</v>
       </c>
       <c r="N2" t="n">
-        <v>9.59832997395597</v>
+        <v>9.548596136424182</v>
       </c>
       <c r="O2" t="n">
-        <v>3.098117165950308</v>
+        <v>3.090080279931928</v>
       </c>
       <c r="P2" t="n">
-        <v>371.4056982667348</v>
+        <v>371.3900557327528</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32923,28 +33119,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2137035916510803</v>
+        <v>-0.2138998093716463</v>
       </c>
       <c r="J3" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K3" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2600828587289626</v>
+        <v>0.2630188853247398</v>
       </c>
       <c r="M3" t="n">
-        <v>2.230446817647885</v>
+        <v>2.218142553942371</v>
       </c>
       <c r="N3" t="n">
-        <v>7.146180426789315</v>
+        <v>7.103241318259931</v>
       </c>
       <c r="O3" t="n">
-        <v>2.673234076318292</v>
+        <v>2.665190672027038</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5785989410201</v>
+        <v>366.5807118089966</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33001,28 +33197,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1845382497637851</v>
+        <v>-0.1837895309101661</v>
       </c>
       <c r="J4" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K4" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2613045829401982</v>
+        <v>0.262252142274482</v>
       </c>
       <c r="M4" t="n">
-        <v>1.849399982214272</v>
+        <v>1.841681895564129</v>
       </c>
       <c r="N4" t="n">
-        <v>5.275157804751656</v>
+        <v>5.245476304944851</v>
       </c>
       <c r="O4" t="n">
-        <v>2.296771169435836</v>
+        <v>2.290300483549015</v>
       </c>
       <c r="P4" t="n">
-        <v>368.0990762091721</v>
+        <v>368.090995911722</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33079,28 +33275,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2254652105373951</v>
+        <v>-0.2242240924082327</v>
       </c>
       <c r="J5" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K5" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.393252473000263</v>
+        <v>0.3934682686259918</v>
       </c>
       <c r="M5" t="n">
-        <v>1.664775055425664</v>
+        <v>1.661702924522044</v>
       </c>
       <c r="N5" t="n">
-        <v>4.297737786868209</v>
+        <v>4.278217305307146</v>
       </c>
       <c r="O5" t="n">
-        <v>2.073098595549235</v>
+        <v>2.06838519268224</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1891700864085</v>
+        <v>368.1757795383592</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33157,28 +33353,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2565082511315251</v>
+        <v>-0.2553309739495465</v>
       </c>
       <c r="J6" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K6" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3922424363332764</v>
+        <v>0.3930205662028039</v>
       </c>
       <c r="M6" t="n">
-        <v>1.94972053547568</v>
+        <v>1.942865769269008</v>
       </c>
       <c r="N6" t="n">
-        <v>5.586280740668021</v>
+        <v>5.558020973580408</v>
       </c>
       <c r="O6" t="n">
-        <v>2.363531413091017</v>
+        <v>2.357545540086216</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1663535327369</v>
+        <v>371.1536511102108</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33235,28 +33431,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1232822402895117</v>
+        <v>-0.1250050299112791</v>
       </c>
       <c r="J7" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K7" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08348690452120155</v>
+        <v>0.08659250545419261</v>
       </c>
       <c r="M7" t="n">
-        <v>2.396258892032613</v>
+        <v>2.389774603604774</v>
       </c>
       <c r="N7" t="n">
-        <v>9.142514020177195</v>
+        <v>9.099001155397961</v>
       </c>
       <c r="O7" t="n">
-        <v>3.023659044961451</v>
+        <v>3.016455064375725</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5344373695367</v>
+        <v>371.5530270830652</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33313,28 +33509,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1328462273058835</v>
+        <v>-0.1348207101260597</v>
       </c>
       <c r="J8" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K8" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1328006841826372</v>
+        <v>0.1375308188398784</v>
       </c>
       <c r="M8" t="n">
-        <v>1.842860321255929</v>
+        <v>1.841041102781384</v>
       </c>
       <c r="N8" t="n">
-        <v>6.31482541841549</v>
+        <v>6.292326588548414</v>
       </c>
       <c r="O8" t="n">
-        <v>2.512931638229638</v>
+        <v>2.50845103371551</v>
       </c>
       <c r="P8" t="n">
-        <v>373.4926407048645</v>
+        <v>373.51394589764</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33391,28 +33587,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1383061830499163</v>
+        <v>-0.1397373604045797</v>
       </c>
       <c r="J9" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K9" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1100596675417171</v>
+        <v>0.1133422887464616</v>
       </c>
       <c r="M9" t="n">
-        <v>2.358312004986823</v>
+        <v>2.350890409474283</v>
       </c>
       <c r="N9" t="n">
-        <v>8.475399303407203</v>
+        <v>8.43225179094906</v>
       </c>
       <c r="O9" t="n">
-        <v>2.911253905692048</v>
+        <v>2.903833981299389</v>
       </c>
       <c r="P9" t="n">
-        <v>368.2132232896527</v>
+        <v>368.2286659771195</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33469,28 +33665,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2148617504278016</v>
+        <v>-0.2204365069158547</v>
       </c>
       <c r="J10" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K10" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1677596764280266</v>
+        <v>0.1755299376506281</v>
       </c>
       <c r="M10" t="n">
-        <v>2.809533944109954</v>
+        <v>2.822063258332189</v>
       </c>
       <c r="N10" t="n">
-        <v>12.54942065629306</v>
+        <v>12.59926502052286</v>
       </c>
       <c r="O10" t="n">
-        <v>3.542516147640411</v>
+        <v>3.549544339844603</v>
       </c>
       <c r="P10" t="n">
-        <v>365.1319128781516</v>
+        <v>365.1920694588003</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33528,7 +33724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K654"/>
+  <dimension ref="A1:K658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70785,6 +70981,234 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.622087571973985,174.76590118360198</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.62180858011318,174.76673173686854</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.62145902316003,174.76751233490174</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.62101988734394,174.76822038152386</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.62056387789541,174.76891288714836</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.62006833138741,174.76955253482726</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-36.619528490978986,174.77012859738767</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-36.61893344144554,174.77062474297492</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>-36.61834706421793,174.77115753771912</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.62208298373126,174.76589831773782</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.621803448110555,174.76672847096242</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.6214563059545,174.76751013556853</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.62101819805649,174.7682187057961</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-36.62056353927708,174.76891251832808</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-36.620066658555444,174.76955034266817</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-36.61952812820851,174.77012795712275</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>-36.6189331316055,174.7706240612706</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>-36.618346754379985,174.77115685601865</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.62208298373126,174.76589831773782</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.621803448110555,174.76672847096242</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.6214563059545,174.76751013556853</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.62102235088809,174.7682228252937</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-36.62056536781608,174.76891450995768</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-36.620066348771736,174.76954993671282</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-36.6195268325996,174.7701256704623</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>-36.618931715193874,174.77062094490807</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>-36.618346975692795,174.77115734294753</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.62208322521773,174.76589846857277</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.621801924547256,174.76672750139664</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.62145607952072,174.76750995229077</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.62102249166202,174.7682229649377</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-36.62056590960541,174.76891510007022</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-36.620066844425665,174.7695505862414</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-36.61952714354573,174.77012621926082</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>-36.61893255618829,174.77062279524833</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>-36.61834741831844,174.77115831680536</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
